--- a/impianti_geocodificati.xlsx
+++ b/impianti_geocodificati.xlsx
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>SCS - Società Canavesana Servizi SpA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>test2</t>
+          <t>CIDIU SpA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -630,7 +630,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>test3</t>
+          <t>CIDIU SpA - Punto Ambiente</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -691,7 +691,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>test4</t>
+          <t>Consorzio Chierese per i Servizi (CCS)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -752,7 +752,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>test5</t>
+          <t>SETA SpA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -813,7 +813,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>test6</t>
+          <t>AMIAT SpA (Gruppo Iren)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -874,7 +874,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>test7</t>
+          <t>CIDIU SpA</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>test8</t>
+          <t>ASSA SpA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -996,7 +996,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>test9</t>
+          <t>ASSA SpA</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1057,7 +1057,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>test10</t>
+          <t>ACSR SpA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1118,7 +1118,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>test11</t>
+          <t>San Carlo Srl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1179,7 +1179,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>test12</t>
+          <t>STR Srl</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1240,7 +1240,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>test13</t>
+          <t>Consorzio Servizi Rifiuti Novese Tortonese Acquese e Ovadese</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1301,7 +1301,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>test14</t>
+          <t>F.lli Boscaro Divisione Ambiente - Biorso</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1362,7 +1362,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>test15</t>
+          <t>ConSer VCO SpA</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>test16</t>
+          <t>ConSer VCO SpA</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1484,7 +1484,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>test17</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1545,7 +1545,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>test18</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1606,7 +1606,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>test19</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1667,7 +1667,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>test20</t>
+          <t>Ricicleco Srl</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1728,7 +1728,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>test21</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1789,7 +1789,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>test22</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1850,7 +1850,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>test23</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1911,7 +1911,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>test24</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1972,7 +1972,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>test25</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2033,7 +2033,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>test26</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2094,7 +2094,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>test27</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2155,7 +2155,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>test28</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2216,7 +2216,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>test29</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2277,7 +2277,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>test30</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2338,7 +2338,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>test31</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2399,7 +2399,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>test32</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2460,7 +2460,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>test33</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2521,7 +2521,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>test34</t>
+          <t>AEMME Linea Ambiente Srl</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2582,7 +2582,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>test35</t>
+          <t>AEMME Linea Ambiente Srl</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2643,7 +2643,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>test36</t>
+          <t>CEM Ambiente SpA</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2704,7 +2704,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>test37</t>
+          <t>CEM Ambiente SpA</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2765,7 +2765,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>test38</t>
+          <t>CEM Ambiente SpA</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2826,7 +2826,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>test39</t>
+          <t>CEM Ambiente SpA</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2887,7 +2887,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>test40</t>
+          <t>AEMME Linea Ambiente Srl</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2948,7 +2948,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>test41</t>
+          <t>CEM Ambiente SpA</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3009,7 +3009,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>test42</t>
+          <t>AMSA SpA (Gruppo A2A)</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3070,7 +3070,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>test43</t>
+          <t>Green Tech Srl</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -3131,7 +3131,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>test44</t>
+          <t>AEMME Linea Ambiente Srl</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3192,7 +3192,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>test45</t>
+          <t>Linea Gestioni Srl</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3253,7 +3253,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>test46</t>
+          <t>Linea Gestioni Srl</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3314,7 +3314,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>test47</t>
+          <t>Linea Gestioni Srl</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3375,7 +3375,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>test48</t>
+          <t>Linea Gestioni Srl</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3436,7 +3436,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>test49</t>
+          <t>Coinger Srl</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3497,7 +3497,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>test50</t>
+          <t>Cogeme SpA</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -3558,7 +3558,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>test51</t>
+          <t>BAS SpA - Bergamo Ambiente e Servizi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3619,7 +3619,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>test52</t>
+          <t>Coinger Srl</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3680,7 +3680,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>test53</t>
+          <t>SEA Servizi e Ambiente SpA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3741,7 +3741,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>test54</t>
+          <t>BAS SpA - Bergamo Ambiente e Servizi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3802,7 +3802,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>test55</t>
+          <t>A2A Ambiente SpA</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3863,7 +3863,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>test56</t>
+          <t>SIEM Srl</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3924,7 +3924,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>test57</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3985,7 +3985,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>test58</t>
+          <t>Cogeme SpA</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -4046,7 +4046,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>test59</t>
+          <t>A2A Ambiente SpA</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -4107,7 +4107,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>test60</t>
+          <t>Cogeme SpA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -4168,7 +4168,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>test61</t>
+          <t>Aprica SpA (Gruppo A2A)</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -4229,7 +4229,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>test62</t>
+          <t>Aprica SpA (Gruppo A2A)</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -4290,7 +4290,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>test63</t>
+          <t>Cogeme SpA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4351,7 +4351,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>test64</t>
+          <t>AGESP SpA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4412,7 +4412,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>test65</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4473,7 +4473,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>test66</t>
+          <t>Padania Acque SpA</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4534,7 +4534,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>test67</t>
+          <t>Tea Acque Srl (Gruppo TEA)</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4595,7 +4595,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>test68</t>
+          <t>Tea Acque Srl (Gruppo TEA)</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -4656,7 +4656,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>test69</t>
+          <t>Tea Acque Srl (Gruppo TEA)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4717,7 +4717,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>test70</t>
+          <t>Tecnogarden Service Srl</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -4778,7 +4778,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>test71</t>
+          <t>Comunità Comprensoriale Oltradige-Bassa Atesina</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -4839,7 +4839,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>test72</t>
+          <t>Comunità Comprensoriale Valle Pusteria</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4900,7 +4900,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>test73</t>
+          <t>Comunità Comprensoriale Valle Pusteria</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4961,7 +4961,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>test74</t>
+          <t>Comunità Comprensoriale Oltradige-Bassa Atesina</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -5022,7 +5022,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>test75</t>
+          <t>ASM Merano - SW Meran SpA</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -5083,7 +5083,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>test76</t>
+          <t>Comunità Comprensoriale Burgraviato</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -5144,7 +5144,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>test77</t>
+          <t>Comunità Comprensoriale Valle Isarco</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -5205,7 +5205,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>test78</t>
+          <t>Comunità Comprensoriale Salto-Sciliar</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -5266,7 +5266,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>test79</t>
+          <t>Comunità Comprensoriale Venosta</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -5327,7 +5327,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>test80</t>
+          <t>Dolomiti Ambiente Srl</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -5388,7 +5388,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>test81</t>
+          <t>Dolomiti Ambiente Srl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -5449,7 +5449,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>test82</t>
+          <t>SERIT Srl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -5510,7 +5510,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>test83</t>
+          <t>Cerea SpA</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -5571,7 +5571,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>test84</t>
+          <t>Agrinord Srl</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5632,7 +5632,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>test85</t>
+          <t>Agrinord Srl</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -5693,7 +5693,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>test86</t>
+          <t>AGNO Srl</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5754,7 +5754,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>test87</t>
+          <t>Valliflor Srl</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -5815,7 +5815,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>test88</t>
+          <t>Biogarda Srl</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5876,7 +5876,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>test89</t>
+          <t>Dal Maso Group Srl</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -5937,7 +5937,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>test90</t>
+          <t>G.I.E. - Gestione Impianti Ecologici Srl</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -5998,7 +5998,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>test91</t>
+          <t>Agno Chiampo Ambiente Srl</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -6059,7 +6059,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>test92</t>
+          <t>G.I.E. - Gestione Impianti Ecologici Srl</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -6120,7 +6120,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>test93</t>
+          <t>Contarina SpA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -6181,7 +6181,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>test94</t>
+          <t>Contarina SpA</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -6242,7 +6242,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>test95</t>
+          <t>Verde Ambiente Srl</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -6303,7 +6303,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>test96</t>
+          <t>Verde Ambiente Srl</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -6364,7 +6364,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>test97</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -6425,7 +6425,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>test98</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -6486,7 +6486,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>test99</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -6547,7 +6547,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>test100</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -6608,7 +6608,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>test101</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -6669,7 +6669,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>test102</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6730,7 +6730,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>test103</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -6791,7 +6791,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>test104</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6852,7 +6852,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>test105</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -6913,7 +6913,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>test106</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -6974,7 +6974,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>test107</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -7035,7 +7035,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>test108</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -7096,7 +7096,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>test109</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -7157,7 +7157,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>test110</t>
+          <t>Gruppo Veritas SpA</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -7218,7 +7218,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>test111</t>
+          <t>ETRA SpA</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -7279,7 +7279,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>test112</t>
+          <t>ETRA SpA</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -7340,7 +7340,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>test113</t>
+          <t>ASM Rovigo SpA</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -7401,7 +7401,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>test114</t>
+          <t>ASM Rovigo SpA</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -7462,7 +7462,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>test115</t>
+          <t>ASM Rovigo SpA</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -7523,7 +7523,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>test116</t>
+          <t>ASM Rovigo SpA</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -7584,7 +7584,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>test117</t>
+          <t>NET SpA</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -7645,7 +7645,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>test118</t>
+          <t>Isontina Ambiente Srl</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -7706,7 +7706,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>test119</t>
+          <t>AcegasApsAmga SpA (Gruppo Hera)</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -7767,7 +7767,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>test120</t>
+          <t>Isontina Ambiente Srl</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -7828,7 +7828,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>test121</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7889,7 +7889,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>test122</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -7950,7 +7950,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>test123</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -8011,7 +8011,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>test124</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -8072,7 +8072,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>test125</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -8133,7 +8133,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>test126</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -8194,7 +8194,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>test127</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -8255,7 +8255,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>test128</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -8316,7 +8316,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>test129</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -8377,7 +8377,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>test130</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -8438,7 +8438,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>test131</t>
+          <t>SNUA Srl</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -8499,7 +8499,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>test132</t>
+          <t>AMAIE Energia e Servizi Srl</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -8560,7 +8560,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>test133</t>
+          <t>Green Recycling Srl</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -8621,7 +8621,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>test134</t>
+          <t>AMIU Genova SpA</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -8682,7 +8682,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>test135</t>
+          <t>AMIU Genova SpA</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -8743,7 +8743,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>test136</t>
+          <t>AMIU Genova SpA</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -8804,7 +8804,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>test137</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8865,7 +8865,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>test138</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -8926,7 +8926,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>test139</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -8987,7 +8987,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>test140</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -9048,7 +9048,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>test141</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -9109,7 +9109,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>test142</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -9170,7 +9170,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>test143</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -9231,7 +9231,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>test144</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -9292,7 +9292,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>test145</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -9353,7 +9353,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>test146</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -9414,7 +9414,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>test147</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -9475,7 +9475,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>test148</t>
+          <t>Cermec SpA</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -9536,7 +9536,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>test149</t>
+          <t>Alia Servizi Ambientali SpA</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -9597,7 +9597,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>test150</t>
+          <t>RetiAmbiente SpA</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -9658,7 +9658,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>test151</t>
+          <t>RetiAmbiente SpA</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -9719,7 +9719,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>test152</t>
+          <t>RetiAmbiente SpA</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -9780,7 +9780,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>test153</t>
+          <t>RetiAmbiente SpA</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -9841,7 +9841,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>test154</t>
+          <t>Sei Toscana Srl</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -9902,7 +9902,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>test155</t>
+          <t>Sienambiente SpA</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -9963,7 +9963,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>test156</t>
+          <t>Sienambiente SpA</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -10024,7 +10024,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>test157</t>
+          <t>Sei Toscana Srl</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -10085,7 +10085,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>test158</t>
+          <t>Sei Toscana Srl</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -10146,7 +10146,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>test159</t>
+          <t>Sei Toscana Srl</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -10207,7 +10207,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>test160</t>
+          <t>Trasimeno Srl</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -10268,7 +10268,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>test161</t>
+          <t>TSA - Trasimeno Servizi Ambientali SpA</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -10329,7 +10329,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>test162</t>
+          <t>Astea SpA</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -10390,7 +10390,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>test163</t>
+          <t>Cosmari Srl</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -10451,7 +10451,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>test164</t>
+          <t>Cosmari Srl</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -10512,7 +10512,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>test165</t>
+          <t>Rap Fermo SpA</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -10573,7 +10573,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>test166</t>
+          <t>Cosp Tecno Service Srl</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -10634,7 +10634,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>test167</t>
+          <t>Cosp Tecno Service Srl</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -10695,7 +10695,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>test168</t>
+          <t>Ecologia Viterbo SpA</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -10756,7 +10756,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>test169</t>
+          <t>Ecologia Viterbo SpA</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -10817,7 +10817,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>test170</t>
+          <t>Cosp Tecno Service Srl</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -10878,7 +10878,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>test171</t>
+          <t>Myoporum Sas</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -10939,7 +10939,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>test172</t>
+          <t>COGEA Srl</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -11000,7 +11000,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>test173</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -11061,7 +11061,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>test174</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -11122,7 +11122,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>test175</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -11183,7 +11183,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>test176</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -11244,7 +11244,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>test177</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -11305,7 +11305,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>test178</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -11366,7 +11366,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>test179</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -11427,7 +11427,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>test180</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -11488,7 +11488,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>test181</t>
+          <t>Ama SpA</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -11549,7 +11549,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>test182</t>
+          <t>Acqualatina SpA</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -11610,7 +11610,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>test183</t>
+          <t>Ares Ambiente Srl</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -11671,7 +11671,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>test184</t>
+          <t>ACIAM SpA</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -11732,7 +11732,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>test185</t>
+          <t>Cesca Sas</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -11793,7 +11793,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>test186</t>
+          <t>Industria Compostaggio Rifiuti Organici Srl</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -11854,7 +11854,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>test187</t>
+          <t>FO.MET.A.L. Srl</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -11915,7 +11915,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>test188</t>
+          <t>Consorzio CIVETA</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -11976,7 +11976,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>test189</t>
+          <t>Giuliano Environment Srl</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -12037,7 +12037,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>test190</t>
+          <t>Ecogestioni Srl</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -12098,7 +12098,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>test191</t>
+          <t>New Vision Srl</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -12159,7 +12159,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>test192</t>
+          <t>SAPNA SpA - Sistema Ambiente Provincia Napoli</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -12220,7 +12220,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>test193</t>
+          <t>SAPNA SpA - Sistema Ambiente Provincia Napoli</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -12281,7 +12281,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>test194</t>
+          <t>IRPINIAMBIENTE SpA</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -12342,7 +12342,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>test195</t>
+          <t>Foggia Ambiente Srl</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -12403,7 +12403,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>test196</t>
+          <t>GAIA Srl</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -12464,7 +12464,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>test197</t>
+          <t>ASECO SpA (Gruppo AQP)</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -12525,7 +12525,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>test198</t>
+          <t>Progeva Srl</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -12586,7 +12586,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>test199</t>
+          <t>Manduriambiente SpA</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -12647,7 +12647,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>test200</t>
+          <t>Kyma Ambiente SpA</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -12708,7 +12708,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>test201</t>
+          <t>Ecolevante Srl</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -12769,7 +12769,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>test202</t>
+          <t>Calabra Maceri e Servizi SpA</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -12830,7 +12830,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>test203</t>
+          <t>Ecologia Oggi SpA</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -12891,7 +12891,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>test204</t>
+          <t>Calabra Maceri e Servizi SpA</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -12952,7 +12952,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>test205</t>
+          <t>Ecologia Oggi SpA</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -13013,7 +13013,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>test206</t>
+          <t>Ecologia Oggi SpA</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -13074,7 +13074,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>test207</t>
+          <t>Ecopiana Srl</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -13135,7 +13135,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>test208</t>
+          <t>TM.E SpA</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -13196,7 +13196,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>test209</t>
+          <t>TM.E SpA</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -13257,7 +13257,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>test210</t>
+          <t>Ecologia Oggi SpA</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -13318,7 +13318,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>test211</t>
+          <t>Salvaguardia Ambientale SpA</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -13379,7 +13379,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>test212</t>
+          <t>Euro Service Italia Srl</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -13440,7 +13440,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>test213</t>
+          <t>Belice Ambiente SpA</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -13501,7 +13501,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>test214</t>
+          <t>SRR Palermo Provincia Nord</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -13562,7 +13562,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>test215</t>
+          <t>RAP SpA - Risorse Ambiente Palermo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -13623,7 +13623,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>test216</t>
+          <t>ME.GA. Srl</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -13684,7 +13684,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>test217</t>
+          <t>GE.S.A. SpA</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -13745,7 +13745,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13770,7 +13770,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>test218</t>
+          <t>GE.S.A. SpA</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -13806,7 +13806,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>test219</t>
+          <t>SO.GE.I.R. SpA</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -13867,7 +13867,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>test220</t>
+          <t>AIMERI Ambiente Srl</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -13928,7 +13928,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>test221</t>
+          <t>RACO Srl</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -13989,7 +13989,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>test222</t>
+          <t>RACO Srl</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -14050,7 +14050,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>test223</t>
+          <t>RACO Srl</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -14111,7 +14111,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>test224</t>
+          <t>RACO Srl</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -14172,7 +14172,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>test225</t>
+          <t>Kalat Impianti Srl</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -14233,7 +14233,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>test226</t>
+          <t>RACO Srl</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -14294,7 +14294,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>test227</t>
+          <t>RACO Srl</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -14355,7 +14355,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>test228</t>
+          <t>Remsicilia SpA</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -14416,7 +14416,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>test229</t>
+          <t>Sicula Compost Srl</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -14477,7 +14477,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>test230</t>
+          <t>Steni Ambiente Srl</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -14538,7 +14538,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>test231</t>
+          <t>Unione dei Comuni Logudoro</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -14599,7 +14599,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>test232</t>
+          <t>CIPNES Gallura / Sarda Compost Srl</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -14660,7 +14660,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>test233</t>
+          <t>CIPNES Gallura / Sarda Compost Srl</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -14721,7 +14721,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>test234</t>
+          <t>Unione dei Comuni Logudoro</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -14782,7 +14782,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>test235</t>
+          <t>Verde Vita Srl</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -14843,7 +14843,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>test236</t>
+          <t>GESAM Srl</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -14904,7 +14904,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>test237</t>
+          <t>GESAM Srl</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -14965,7 +14965,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>test238</t>
+          <t>Unione dei Comuni Alta Gallura</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -15026,7 +15026,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>test239</t>
+          <t>Consorzio di Nuoro - Pratosardo</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -15087,7 +15087,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>test240</t>
+          <t>Ogliastra Compost Srl</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -15148,7 +15148,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>test241</t>
+          <t>CACIP SpA</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -15209,7 +15209,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>test242</t>
+          <t>PRO.MI.S.A. Srl</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -15270,7 +15270,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>test243</t>
+          <t>CACIP SpA</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -15331,7 +15331,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>test244</t>
+          <t>Consorzio Industriale Provinciale Oristanese</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -15392,7 +15392,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>test245</t>
+          <t>Comune di Carbonia</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -15453,7 +15453,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>test246</t>
+          <t>Sardarec Srl (IRS)</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -15514,7 +15514,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>test247</t>
+          <t>Alberghina Verde Srl</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -15575,7 +15575,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>test248</t>
+          <t>CISA Srl</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -15627,16 +15627,16 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>39.4390511</v>
+        <v>39.42404</v>
       </c>
       <c r="O249" t="n">
-        <v>9.0093736</v>
+        <v>8.923138</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>test249</t>
+          <t>Consorzio Industriale Provinciale Villacidro</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -15697,7 +15697,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Compostaggio</t>
+          <t>Compostaggio</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>test250</t>
+          <t>Ecosardinia Srl</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -15758,7 +15758,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>test251</t>
+          <t>Acea Pinerolese Industriale SpA</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -15819,7 +15819,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>test252</t>
+          <t>Territorio e Risorse Srl (Gruppo Iren)</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -15880,7 +15880,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>test253</t>
+          <t>Koster AB Srl</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -15941,7 +15941,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>test254</t>
+          <t>San Carlo Srl</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -16002,7 +16002,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>test255</t>
+          <t>GAIA SpA</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -16063,7 +16063,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>test256</t>
+          <t>Bioland Srl</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -16124,7 +16124,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>test257</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -16185,7 +16185,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>test258</t>
+          <t>A2A Ambiente SpA</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -16246,7 +16246,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>test259</t>
+          <t>Ecoprogetto Milano Srl (Gruppo Ladurner)</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -16307,7 +16307,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>test260</t>
+          <t>Green Tech Srl</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -16368,7 +16368,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>test261</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -16429,7 +16429,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>test262</t>
+          <t>Linea Gestioni Srl</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -16490,7 +16490,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>test263</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -16551,7 +16551,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>test264</t>
+          <t>Padania Acque SpA</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -16612,7 +16612,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>test265</t>
+          <t>SILEA SpA</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -16673,7 +16673,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>test266</t>
+          <t>BIOMET SpA</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -16734,7 +16734,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>test267</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -16795,7 +16795,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16820,7 +16820,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>test268</t>
+          <t>EAL Compost Srl</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -16856,7 +16856,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>test269</t>
+          <t>Dolomiti Ambiente Srl</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -16917,7 +16917,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>test270</t>
+          <t>Agrofert Srl</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -16978,7 +16978,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17003,7 +17003,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>test271</t>
+          <t>Cerea SpA</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -17039,7 +17039,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>test272</t>
+          <t>ETRA SpA</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -17100,7 +17100,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>test273</t>
+          <t>Contarina SpA</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -17161,7 +17161,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>test274</t>
+          <t>Contarina SpA</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -17222,7 +17222,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>test275</t>
+          <t>ETRA SpA</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -17283,7 +17283,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>test276</t>
+          <t>Bioman SpA</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -17344,7 +17344,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17369,7 +17369,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>test277</t>
+          <t>Bioman SpA</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -17405,7 +17405,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>test278</t>
+          <t>SAT - Servizi Ambientali Territoriali Srl</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -17466,7 +17466,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>test279</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -17527,7 +17527,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>test280</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -17588,7 +17588,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>test281</t>
+          <t>AIMAG SpA</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -17649,7 +17649,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>test282</t>
+          <t>Geovest SpA</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -17710,7 +17710,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>test283</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -17771,7 +17771,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>test284</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -17832,7 +17832,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>test285</t>
+          <t>Clara SpA</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -17893,7 +17893,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>test286</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -17954,7 +17954,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>test287</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -18015,7 +18015,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>test288</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -18076,7 +18076,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18101,7 +18101,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>test289</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -18137,7 +18137,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>test290</t>
+          <t>Alia Servizi Ambientali SpA</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -18198,7 +18198,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>test291</t>
+          <t>Sei Toscana Srl</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -18259,7 +18259,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>test292</t>
+          <t>Sienambiente SpA</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -18320,7 +18320,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>test293</t>
+          <t>RetiAmbiente SpA</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -18381,7 +18381,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>test294</t>
+          <t>Sogepu SpA</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -18442,7 +18442,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>test295</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -18503,7 +18503,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>test296</t>
+          <t>ASM Terni SpA</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -18564,7 +18564,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>test297</t>
+          <t>Orvieto Ambiente Srl</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -18625,7 +18625,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>test298</t>
+          <t>En Ergon Srl (Gruppo Astea)</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -18686,7 +18686,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>test299</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -18747,7 +18747,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>test300</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -18808,7 +18808,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>test301</t>
+          <t>Acqualatina SpA</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -18869,7 +18869,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>test302</t>
+          <t>ACIAM SpA</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -18930,7 +18930,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>test303</t>
+          <t>CTIP BLU Srl</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -18991,7 +18991,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>test304</t>
+          <t>SAPNA SpA - Sistema Ambiente Provincia Napoli</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -19052,7 +19052,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>test305</t>
+          <t>SAPNA SpA - Sistema Ambiente Provincia Napoli</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -19113,7 +19113,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>test306</t>
+          <t>Salerno Pulita SpA</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -19174,7 +19174,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>test307</t>
+          <t>AMIU Puglia SpA</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -19235,7 +19235,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>test308</t>
+          <t>Tersan Puglia SpA</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -19296,7 +19296,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>test309</t>
+          <t>Kyma Ambiente SpA</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -19357,7 +19357,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>test310</t>
+          <t>Progeva Srl</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -19418,7 +19418,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>test311</t>
+          <t>Ecolevante Srl</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -19479,7 +19479,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>test312</t>
+          <t>Ecologia Oggi SpA</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -19540,7 +19540,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19565,7 +19565,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>test313</t>
+          <t>Calabra Maceri e Servizi SpA</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -19601,7 +19601,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>test314</t>
+          <t>Ecologia Oggi SpA</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -19662,7 +19662,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>test315</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -19723,7 +19723,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Trattamento integrato aerobico e anaerobico</t>
+          <t>Trattamento integrato aerobico e anaerobico</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>test316</t>
+          <t>Bioenerys</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -19784,7 +19784,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>test317</t>
+          <t>Consorzio Servizi Rifiuti Novese Tortonese Acquese e Ovadese</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -19845,7 +19845,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19870,7 +19870,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>test318</t>
+          <t>Econord SpA</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -19906,7 +19906,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>test319</t>
+          <t>Industrie Chimiche Forestali SpA (processo Biosip-Agatos)</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -19967,7 +19967,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>test320</t>
+          <t>AMSA SpA (Gruppo A2A)</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -20028,7 +20028,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20053,7 +20053,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>test321</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -20089,7 +20089,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>test322</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -20150,7 +20150,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>test323</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -20211,7 +20211,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20236,7 +20236,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>test324</t>
+          <t>Padania Acque SpA</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -20272,7 +20272,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>test325</t>
+          <t>Tea Acque Srl (Gruppo TEA)</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -20333,7 +20333,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20358,7 +20358,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>test326</t>
+          <t>Tea Acque Srl (Gruppo TEA)</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -20394,7 +20394,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>test327</t>
+          <t>Tea Acque Srl (Gruppo TEA)</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -20455,7 +20455,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>test328</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -20516,7 +20516,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>test329</t>
+          <t>Iren Ambiente SpA</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -20577,7 +20577,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>test330</t>
+          <t>Comunità Comprensoriale Alta Pusteria</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -20638,7 +20638,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>test331</t>
+          <t>Comunità Comprensoriale Burgraviato</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -20699,7 +20699,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>test332</t>
+          <t>Dolomiti Ambiente Srl</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -20760,7 +20760,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20785,7 +20785,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>test333</t>
+          <t>AGSM AIM SpA</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -20821,7 +20821,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>test334</t>
+          <t>Cerea SpA</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -20882,7 +20882,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>test335</t>
+          <t>ETRA SpA</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -20943,7 +20943,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>test336</t>
+          <t>Contarina SpA</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -21004,7 +21004,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>test337</t>
+          <t>ETRA SpA</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -21065,7 +21065,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>test338</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -21126,7 +21126,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>test339</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -21187,7 +21187,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21212,7 +21212,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>test340</t>
+          <t>HERAmbiente SpA</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -21248,7 +21248,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>test341</t>
+          <t>Latina Ambiente SpA</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -21309,7 +21309,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>test342</t>
+          <t>Latina Ambiente SpA</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -21370,7 +21370,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21395,7 +21395,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>test343</t>
+          <t>Foglia Umberto Srl</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -21431,7 +21431,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Digestione anaerobica</t>
+          <t>Digestione anaerobica</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>test344</t>
+          <t>Foglia Umberto Srl</t>
         </is>
       </c>
       <c r="G345" t="n">
